--- a/Assets/Data/Excel/excel_text_story[故事文本].xlsx
+++ b/Assets/Data/Excel/excel_text_story[故事文本].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="TextStory" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -98,10 +98,55 @@
     <t>string</t>
   </si>
   <si>
-    <t>名字</t>
+    <t>文本编号</t>
   </si>
   <si>
-    <t>内容</t>
+    <t>//类型 0默认文本 1选择对话    4书本详情  5黑幕标题  99默认</t>
+  </si>
+  <si>
+    <t>文本顺序</t>
+  </si>
+  <si>
+    <t>指定下一顺序</t>
+  </si>
+  <si>
+    <t>对话类型 0普通对话，1送礼回复对话  2招募对话  3后续对话  4第一次对话</t>
+  </si>
+  <si>
+    <t>文本发起对象ID</t>
+  </si>
+  <si>
+    <t>触发条件 好感区间</t>
+  </si>
+  <si>
+    <t>选择对话 的类型 0提示文本  1选项</t>
+  </si>
+  <si>
+    <t>增加的好感</t>
+  </si>
+  <si>
+    <t>小游戏的前置数据</t>
+  </si>
+  <si>
+    <t>奖励物品</t>
+  </si>
+  <si>
+    <t>停留时间</t>
+  </si>
+  <si>
+    <t>是否停止时间</t>
+  </si>
+  <si>
+    <t>场景人物表情</t>
+  </si>
+  <si>
+    <t>支付条件</t>
+  </si>
+  <si>
+    <t>文本发起人名字</t>
+  </si>
+  <si>
+    <t>文本内容</t>
   </si>
   <si>
     <t>AddItems:210123|AddItems:210124|AddItems:110124|</t>
@@ -132,11 +177,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="10.5"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -586,19 +630,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -607,7 +651,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -731,9 +775,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1086,7 +1133,7 @@
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="23.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="4" max="4" width="18.875" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
@@ -1227,66 +1274,66 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" ht="96.75" spans="1:20">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R3" t="s">
-        <v>17</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="T3" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -5927,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="N96" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="O96">
         <v>5</v>
@@ -8280,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="N143" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -8465,7 +8512,7 @@
         <v>0</v>
       </c>
       <c r="Q147" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S147" s="1">
         <v>300000010003002</v>
